--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,81 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5486,8 +5640,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U22"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5510,1354 +5668,2028 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈 타령 — 민요채보-2/돈 타령.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">돈 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나
-―
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">나
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">약</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">갑</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="P3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+          </r>
+        </is>
+      </c>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+          </r>
+        </is>
+      </c>
+      <c r="S3" s="23"/>
+      <c r="T3" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="U3" s="23"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="Q4" s="26"/>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="25"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="25"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="27"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="S5" s="27"/>
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="U5" s="27"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">혼</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">즉</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="P6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
+      <c r="S6" s="23"/>
+      <c r="T6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
 無
-―</t>
-        </is>
-      </c>
-      <c r="U6" s="3"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U6" s="23"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="O7" s="25"/>
+      <c r="P7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="Q7" s="26"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="S7" s="25"/>
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="27"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="Q8" s="27"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="S8" s="27"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U8" s="27"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="28"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="28"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="28"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="28"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="28"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="28"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O9" s="28"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q9" s="28"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="S9" s="28"/>
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 ○</t>
         </is>
       </c>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="U9" s="28"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 㳞</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無
 姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無
 仲</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="S10" s="25"/>
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲
 㳞</t>
-        </is>
-      </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U10" s="25"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="27"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="27"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="S11" s="27"/>
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈 타령 — 민요채보-2/돈 타령.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="U11" s="27"/>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">돈 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C13"/>
+      <c s="8" r="D13"/>
+      <c s="8" r="E13"/>
+      <c s="8" r="F13"/>
+      <c s="8" r="G13"/>
+      <c s="8" r="H13"/>
+      <c s="8" r="I13"/>
+      <c s="8" r="J13"/>
+      <c s="8" r="K13"/>
+      <c s="8" r="L13"/>
+      <c s="8" r="M13"/>
+      <c s="8" r="N13"/>
+      <c s="8" r="O13"/>
+      <c s="8" r="P13"/>
+      <c s="8" r="Q13"/>
+      <c s="8" r="R13"/>
+      <c s="8" r="S13"/>
+      <c s="8" r="T13"/>
+      <c s="8" r="U13"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="22"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="P14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="T14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="22"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="M15" s="25"/>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+          </r>
+        </is>
+      </c>
+      <c r="O15" s="25"/>
+      <c r="P15" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+          </r>
+        </is>
+      </c>
+      <c r="S15" s="25"/>
+      <c r="T15" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U15" s="25"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="22"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="M16" s="27"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="O16" s="27"/>
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="Q16" s="27"/>
+      <c r="R16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="S16" s="27"/>
+      <c r="T16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="U16" s="27"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="22"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">억</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="P17" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">번</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="R17" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="T17" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="22"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="M18" s="25"/>
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="O18" s="25"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="Q18" s="25"/>
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="S18" s="25"/>
+      <c r="T18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="U18" s="25"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="22"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="M19" s="27"/>
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲
 㳞</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="O19" s="27"/>
+      <c r="P19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="Q19" s="27"/>
+      <c r="R19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="S19" s="27"/>
+      <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U19" s="27"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="22"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="M20" s="28"/>
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="O20" s="28"/>
+      <c r="P20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="Q20" s="28"/>
+      <c r="R20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="S20" s="28"/>
+      <c r="T20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="U20" s="28"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="22"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="M21" s="25"/>
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 㳞</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="O21" s="25"/>
+      <c r="P21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢
 㳞</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="Q21" s="25"/>
+      <c r="R21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="S21" s="25"/>
+      <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="U21" s="25"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="22"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="M22" s="27"/>
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="O22" s="27"/>
+      <c r="P22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="Q22" s="27"/>
+      <c r="R22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="S22" s="27"/>
+      <c r="T22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
+      <c r="U22" s="27"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B13:U13"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="11" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5173,1145 +5214,1145 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">돈 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제녁</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">당신</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">비는</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나는</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">둘이</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">갑돌이</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="U3" s="8"/>
+      <c r="U3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">앗일</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">주이</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">둘</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">둘</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="24"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="24"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">안이기거</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">항것나</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">항것수우</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">갑돌이</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">돈이</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無</t>
         </is>
       </c>
-      <c r="U6" s="8"/>
+      <c r="U6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 太</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 太</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="U7" s="9"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="27"/>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="24"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">난줄</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃피</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">벌나</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화초</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못살</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서로</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="R9" s="18" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">황</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="U9" s="8"/>
+      <c r="U9" s="24"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">겟</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U10" s="9"/>
+      <c r="U10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="27"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑
 㳞</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">새가울</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑
 㳞</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑
 㳞</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑
 㳞</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나아</t>
         </is>
       </c>
-      <c r="R11" s="18" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="S11" s="13" t="inlineStr">
+      <c r="S11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="T11" s="18" t="inlineStr">
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="U11" s="13"/>
+      <c r="U11" s="28"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="24"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="24"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="Q12" s="24"/>
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="S12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="T12" s="18" t="inlineStr">
+      <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U12" s="11"/>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U13" s="9"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="S14" s="27"/>
+      <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -5187,32 +5187,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="U9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="U11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -6218,137 +6218,137 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="25"/>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="25"/>
       <c r="T13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="G14" s="27"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="K14" s="27"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="M14" s="27"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="O14" s="27"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="Q14" s="27"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="S14" s="27"/>
       <c r="T14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -988,13 +988,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1463,13 +1462,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1926,13 +1924,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2394,13 +2391,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2864,13 +2860,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -3332,13 +3327,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3806,13 +3800,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -4274,13 +4267,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4733,13 +4725,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I109" s="2"/>
@@ -5165,13 +5156,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I121" s="2"/>
@@ -6285,71 +6275,61 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="27"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="27"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="27"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="27"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S14" s="27"/>
       <c r="T14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U14" s="27"/>

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -5246,7 +5246,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">제녁</t>
+          <t xml:space="preserve">제
+녁</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -5257,7 +5258,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">당신</t>
+          <t xml:space="preserve">당
+신</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -5268,7 +5270,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">비는</t>
+          <t xml:space="preserve">비
+는</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -5279,7 +5282,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">나는</t>
+          <t xml:space="preserve">나
+는</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -5290,7 +5294,8 @@
       </c>
       <c r="M3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리</t>
+          <t xml:space="preserve">우
+리</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -5301,7 +5306,8 @@
       </c>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">둘이</t>
+          <t xml:space="preserve">둘
+이</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -5312,7 +5318,9 @@
       </c>
       <c r="Q3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">갑돌이</t>
+          <t xml:space="preserve">갑
+돌
+이</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
@@ -5350,7 +5358,8 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">앗일</t>
+          <t xml:space="preserve">앗
+일</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
@@ -5371,7 +5380,8 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주이</t>
+          <t xml:space="preserve">주
+이</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
@@ -5553,7 +5563,10 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">안이기거</t>
+          <t xml:space="preserve">안
+이
+기
+거</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -5564,7 +5577,9 @@
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">항것나</t>
+          <t xml:space="preserve">항
+것
+나</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -5586,7 +5601,10 @@
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">항것수우</t>
+          <t xml:space="preserve">항
+것
+수
+우</t>
         </is>
       </c>
       <c r="N6" s="23" t="inlineStr">
@@ -5597,7 +5615,8 @@
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="P6" s="23" t="inlineStr">
@@ -5608,7 +5627,9 @@
       </c>
       <c r="Q6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">갑돌이</t>
+          <t xml:space="preserve">갑
+돌
+이</t>
         </is>
       </c>
       <c r="R6" s="23" t="inlineStr">
@@ -5618,7 +5639,8 @@
       </c>
       <c r="S6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">돈이</t>
+          <t xml:space="preserve">돈
+이</t>
         </is>
       </c>
       <c r="T6" s="23" t="inlineStr">
@@ -5827,7 +5849,8 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">난줄</t>
+          <t xml:space="preserve">난
+줄</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -5838,7 +5861,8 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃피</t>
+          <t xml:space="preserve">꽃
+피</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -5849,7 +5873,8 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">벌나</t>
+          <t xml:space="preserve">벌
+나</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -5860,7 +5885,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">화초</t>
+          <t xml:space="preserve">화
+초</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -5871,7 +5897,8 @@
       </c>
       <c r="M9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">못살</t>
+          <t xml:space="preserve">못
+살</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -5882,7 +5909,8 @@
       </c>
       <c r="O9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">서로</t>
+          <t xml:space="preserve">서
+로</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -6041,7 +6069,9 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">새가울</t>
+          <t xml:space="preserve">새
+가
+울</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -6101,7 +6131,8 @@
       </c>
       <c r="Q11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">나아</t>
+          <t xml:space="preserve">나
+아</t>
         </is>
       </c>
       <c r="R11" s="21" t="inlineStr">

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5237,14 +5260,14 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">제
 녁</t>
@@ -5256,7 +5279,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">당
 신</t>
@@ -5268,7 +5291,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">비
 는</t>
@@ -5280,7 +5303,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 는</t>
@@ -5292,7 +5315,7 @@
 仲</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 리</t>
@@ -5304,7 +5327,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">둘
 이</t>
@@ -5316,7 +5339,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">갑
 돌
@@ -5329,7 +5352,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -5340,7 +5363,7 @@
 仲</t>
         </is>
       </c>
-      <c r="U3" s="24"/>
+      <c r="U3" s="30"/>
     </row>
     <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
@@ -5350,13 +5373,13 @@
 無</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">앗
 일</t>
@@ -5368,7 +5391,7 @@
 無</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
@@ -5378,7 +5401,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">주
 이</t>
@@ -5390,7 +5413,7 @@
 無</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5400,7 +5423,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">둘</t>
         </is>
@@ -5411,7 +5434,7 @@
 無</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">둘</t>
         </is>
@@ -5421,7 +5444,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5432,7 +5455,7 @@
 無</t>
         </is>
       </c>
-      <c r="S4" s="25" t="inlineStr">
+      <c r="S4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -5442,7 +5465,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="U4" s="25"/>
+      <c r="U4" s="31"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -5451,13 +5474,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5467,7 +5490,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5477,7 +5500,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5487,7 +5510,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5497,7 +5520,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5507,7 +5530,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5517,7 +5540,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5527,7 +5550,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S5" s="27" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -5537,7 +5560,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U5" s="27"/>
+      <c r="U5" s="33"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -5547,21 +5570,21 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">안
 이
@@ -5575,7 +5598,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">항
 것
@@ -5588,7 +5611,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
@@ -5599,7 +5622,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">항
 것
@@ -5613,7 +5636,7 @@
 無</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
@@ -5625,7 +5648,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">갑
 돌
@@ -5637,7 +5660,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">돈
 이</t>
@@ -5649,7 +5672,7 @@
 無</t>
         </is>
       </c>
-      <c r="U6" s="24"/>
+      <c r="U6" s="30"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -5659,21 +5682,21 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5683,7 +5706,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5694,7 +5717,7 @@
 南</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5704,7 +5727,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5715,7 +5738,7 @@
 太</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5726,7 +5749,7 @@
 太</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5737,7 +5760,7 @@
 姑</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -5747,7 +5770,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="U7" s="25"/>
+      <c r="U7" s="31"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -5756,25 +5779,25 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5784,7 +5807,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5794,13 +5817,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="33"/>
       <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5810,7 +5833,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5820,7 +5843,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -5830,7 +5853,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U8" s="27"/>
+      <c r="U8" s="33"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -5840,14 +5863,14 @@
 㳞</t>
         </is>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">난
 줄</t>
@@ -5859,7 +5882,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃
 피</t>
@@ -5871,7 +5894,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">벌
 나</t>
@@ -5883,7 +5906,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화
 초</t>
@@ -5895,7 +5918,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 살</t>
@@ -5907,7 +5930,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 로</t>
@@ -5919,7 +5942,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5930,7 +5953,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">황</t>
         </is>
@@ -5941,7 +5964,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="U9" s="24"/>
+      <c r="U9" s="30"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -5950,13 +5973,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5966,7 +5989,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5976,7 +5999,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5986,7 +6009,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5996,7 +6019,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">겟</t>
         </is>
@@ -6006,7 +6029,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -6016,7 +6039,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -6026,7 +6049,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6036,7 +6059,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U10" s="25"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -6047,7 +6070,7 @@
 無</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
@@ -6055,7 +6078,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -6067,7 +6090,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">새
 가
@@ -6081,7 +6104,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
@@ -6093,7 +6116,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
@@ -6105,7 +6128,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -6117,7 +6140,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O11" s="27" t="inlineStr">
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -6129,7 +6152,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 아</t>
@@ -6142,7 +6165,7 @@
 無</t>
         </is>
       </c>
-      <c r="S11" s="28" t="inlineStr">
+      <c r="S11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -6154,7 +6177,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="U11" s="28"/>
+      <c r="U11" s="34"/>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
@@ -6163,13 +6186,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -6179,7 +6202,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -6189,7 +6212,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -6199,13 +6222,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="30"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="24" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -6215,19 +6238,19 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="24"/>
+      <c r="O12" s="30"/>
       <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="24"/>
+      <c r="Q12" s="30"/>
       <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S12" s="24" t="inlineStr">
+      <c r="S12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -6237,7 +6260,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U12" s="22"/>
+      <c r="U12" s="29"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -6246,61 +6269,61 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U13" s="25"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -6309,61 +6332,61 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="33"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="33"/>
       <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U14" s="27"/>
+      <c r="U14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -641,10 +641,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -587,17 +587,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -714,7 +714,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -768,6 +768,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4886,722 +4926,722 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="7" t="s">
+      <c r="S3" s="18"/>
+      <c r="T3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="U3" s="18"/>
+    </row>
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="9" t="s">
+      <c r="H4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="9" t="s">
+      <c r="L4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="P4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="9" t="s">
+      <c r="P4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="S4" s="19"/>
+      <c r="T4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="J5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="10" t="s">
+      <c r="N5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="7" t="s">
+      <c r="R5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="S5" s="20"/>
+      <c r="T5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="U5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="7" t="s">
+      <c r="S6" s="22"/>
+      <c r="T6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="U6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="U6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="D7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="9" t="s">
+      <c r="H7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="9" t="s">
+      <c r="L7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="9" t="s">
+      <c r="P7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="S7" s="9"/>
-      <c r="T7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="U7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="S7" s="19"/>
+      <c r="T7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="R8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="7" t="s">
+      <c r="S8" s="20"/>
+      <c r="T8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="U8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="U8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="7" t="s">
+      <c r="S9" s="18"/>
+      <c r="T9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="U9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="9" t="s">
+      <c r="J10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="N10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="9" t="s">
+      <c r="N10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="S10" s="9"/>
-      <c r="T10" s="7" t="s">
+      <c r="S10" s="19"/>
+      <c r="T10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="U10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="R11" s="11" t="s">
+      <c r="R11" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="13"/>
-      <c r="T11" s="7" t="s">
+      <c r="S11" s="23"/>
+      <c r="T11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="U11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="U11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R12" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="11" t="s">
+      <c r="R12" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="S12" s="22"/>
+      <c r="T12" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="U12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="U12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="19"/>
+      <c r="H13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="19"/>
+      <c r="L13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="19"/>
+      <c r="N13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="19"/>
+      <c r="P13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="7" t="s">
+      <c r="Q13" s="19"/>
+      <c r="R13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="7" t="s">
+      <c r="S13" s="19"/>
+      <c r="T13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="U13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
+      <c r="U13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="20"/>
+      <c r="F14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="20"/>
+      <c r="H14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="20"/>
+      <c r="J14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11" t="s">
+      <c r="K14" s="20"/>
+      <c r="L14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="23"/>
+      <c r="N14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="20"/>
+      <c r="P14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="7" t="s">
+      <c r="Q14" s="20"/>
+      <c r="R14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="7" t="s">
+      <c r="S14" s="20"/>
+      <c r="T14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5609,7 +5649,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/돈 타령.xlsx
+++ b/sheets/민요/검수/돈 타령.xlsx
@@ -4932,30 +4932,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="80.0" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="T2" s="16"/>
       <c r="U2" s="16"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B3" s="17" t="s">
         <v>53</v>
       </c>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="U3" s="18"/>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B4" s="17" t="s">
         <v>62</v>
       </c>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="U4" s="19"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B5" s="17" t="s">
         <v>48</v>
       </c>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="U5" s="20"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B6" s="17" t="s">
         <v>64</v>
       </c>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="U6" s="18"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B7" s="17" t="s">
         <v>67</v>
       </c>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="U7" s="19"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B8" s="17" t="s">
         <v>68</v>
       </c>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="U8" s="20"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B9" s="17" t="s">
         <v>70</v>
       </c>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="U9" s="18"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="U10" s="19"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B11" s="17" t="s">
         <v>73</v>
       </c>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="U11" s="20"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B12" s="17" t="s">
         <v>48</v>
       </c>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B13" s="17" t="s">
         <v>58</v>
       </c>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="U13" s="19"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B14" s="21" t="s">
         <v>58</v>
       </c>
@@ -5649,7 +5649,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
